--- a/semSix.xlsx
+++ b/semSix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\education\6 семестр\модел\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDADA54A-85C5-4E36-B2F1-F0677A17A852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E628D5-149D-486B-945B-D612E9D75DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="540" firstSheet="4" activeTab="13" xr2:uid="{A13E42BC-86E1-49A4-8600-539A8349C4B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="540" firstSheet="4" activeTab="14" xr2:uid="{A13E42BC-86E1-49A4-8600-539A8349C4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="практика по УП" sheetId="9" state="hidden" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="куб" sheetId="4" state="hidden" r:id="rId12"/>
     <sheet name="29,01модельЛинейная" sheetId="1" state="hidden" r:id="rId13"/>
     <sheet name="30,01модельКривая" sheetId="2" r:id="rId14"/>
-    <sheet name="Сети1" sheetId="5" r:id="rId15"/>
+    <sheet name="Лист4" sheetId="16" r:id="rId15"/>
+    <sheet name="Сети1" sheetId="5" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="6" hidden="1">1</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="252">
   <si>
     <t>i</t>
   </si>
@@ -706,12 +707,114 @@
   <si>
     <t>A1/$A$18</t>
   </si>
+  <si>
+    <t>Места в очереди</t>
+  </si>
+  <si>
+    <t>0МО</t>
+  </si>
+  <si>
+    <t>1МО</t>
+  </si>
+  <si>
+    <t>2МО</t>
+  </si>
+  <si>
+    <t>3МО</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Значение</t>
+  </si>
+  <si>
+    <t>Системы</t>
+  </si>
+  <si>
+    <t>Пропускная способность</t>
+  </si>
+  <si>
+    <t>Вероятность обслуживания</t>
+  </si>
+  <si>
+    <t>Вероятность отказа</t>
+  </si>
+  <si>
+    <t>Вероятность занятости Одного КО</t>
+  </si>
+  <si>
+    <t>Вероятность занятости Двух КО</t>
+  </si>
+  <si>
+    <t>Среднее количество занятых каналов</t>
+  </si>
+  <si>
+    <t>Вероятность простоя Первого КО</t>
+  </si>
+  <si>
+    <t>Вероятность простоя Второго КО</t>
+  </si>
+  <si>
+    <t>Среднее время ожидания заявки в очереди</t>
+  </si>
+  <si>
+    <t>Среднее время нахождение заявок в очереди</t>
+  </si>
+  <si>
+    <t>Среднее время обслуживания заявок в очереди</t>
+  </si>
+  <si>
+    <t>Среднее количество заявок в очереди</t>
+  </si>
+  <si>
+    <t>Вероятность 0 заявок в очереди</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятность 1 заявок в очереди </t>
+  </si>
+  <si>
+    <t>Вероятность 2 заявок в очереди</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятность 3 заявок в очереди </t>
+  </si>
+  <si>
+    <t>Интересы</t>
+  </si>
+  <si>
+    <t>Владелец</t>
+  </si>
+  <si>
+    <t>Клиент</t>
+  </si>
+  <si>
+    <t>Совет</t>
+  </si>
+  <si>
+    <t>0 мест</t>
+  </si>
+  <si>
+    <t>1 место</t>
+  </si>
+  <si>
+    <t>2 места</t>
+  </si>
+  <si>
+    <t>3 места</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -783,6 +886,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -816,7 +926,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -1555,11 +1665,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1793,6 +1927,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5826,304 +6032,304 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0.33333333333333331</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.2857142857142857</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.36363636363636365</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.38461538461538464</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.47058823529411764</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.44444444444444442</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.42105263157894735</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.42857142857142855</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.45454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.47826086956521741</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.42857142857142855</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.375</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.44444444444444442</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="24">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.54545454545454541</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.58333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.61538461538461542</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.6428571428571429</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.66666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.6875</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.6470588235294118</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.66666666666666663</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.63157894736842102</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.61904761904761907</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.63636363636363635</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.60869565217391308</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.58333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.56000000000000005</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.53846153846153844</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0.51851851851851849</c:v>
                 </c:pt>
                 <c:pt idx="27">
+                  <c:v>0.5357142857142857</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.55172413793103448</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.56666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.58064516129032262</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.5625</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.5757575757575758</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.55882352941176472</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.5714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.54054054054054057</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.55263157894736847</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.53846153846153844</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.52500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.51219512195121952</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.52380952380952384</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.53488372093023251</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.52272727272727271</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.51111111111111107</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.52173913043478259</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.53191489361702127</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.54166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.55102040816326525</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.52941176470588236</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51923076923076927</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.50943396226415094</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.51851851851851849</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.50909090909090904</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.5178571428571429</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.50877192982456143</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.48275862068965519</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.46666666666666667</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.4838709677419355</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.48484848484848486</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.47058823529411764</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.48571428571428571</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.48648648648648651</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.47368421052631576</c:v>
-                </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="58">
+                  <c:v>0.49152542372881358</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.48333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.47540983606557374</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.46774193548387094</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.46031746031746029</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.46875</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>0.46153846153846156</c:v>
                 </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.43902439024390244</c:v>
-                </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="65">
+                  <c:v>0.46969696969696972</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.46268656716417911</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.45588235294117646</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.44927536231884058</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.44285714285714284</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.45070422535211269</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.44444444444444442</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.43835616438356162</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.44594594594594594</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.43421052631578949</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>0.42857142857142855</c:v>
                 </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.41860465116279072</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.40909090909090912</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.39130434782608697</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.40425531914893614</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.39583333333333331</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.38775510204081631</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.37254901960784315</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.38461538461538464</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.37735849056603776</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.3888888888888889</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.38181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.39285714285714285</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.38596491228070173</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.39655172413793105</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.40677966101694918</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.4098360655737705</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.40322580645161288</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.41269841269841268</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.40625</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.39393939393939392</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.38805970149253732</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.39705882352941174</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.39130434782608697</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.39436619718309857</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.40277777777777779</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.39726027397260272</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.40540540540540543</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.41333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.40789473684210525</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.41558441558441561</c:v>
-                </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.41025641025641024</c:v>
+                  <c:v>0.42307692307692307</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.4050632911392405</c:v>
+                  <c:v>0.41772151898734178</c:v>
                 </c:pt>
                 <c:pt idx="79">
                   <c:v>0.41249999999999998</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.40740740740740738</c:v>
+                  <c:v>0.41975308641975306</c:v>
                 </c:pt>
                 <c:pt idx="81">
                   <c:v>0.41463414634146339</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.42168674698795183</c:v>
+                  <c:v>0.40963855421686746</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.41666666666666669</c:v>
+                  <c:v>0.40476190476190477</c:v>
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>0.41176470588235292</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.41860465116279072</c:v>
+                  <c:v>0.40697674418604651</c:v>
                 </c:pt>
                 <c:pt idx="86">
                   <c:v>0.41379310344827586</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.40909090909090912</c:v>
+                  <c:v>0.42045454545454547</c:v>
                 </c:pt>
                 <c:pt idx="88">
                   <c:v>0.4157303370786517</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.41111111111111109</c:v>
+                  <c:v>0.42222222222222222</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.40659340659340659</c:v>
+                  <c:v>0.42857142857142855</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.41304347826086957</c:v>
+                  <c:v>0.42391304347826086</c:v>
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>0.41935483870967744</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.41489361702127658</c:v>
+                  <c:v>0.42553191489361702</c:v>
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>0.42105263157894735</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.42708333333333331</c:v>
+                  <c:v>0.41666666666666669</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.42268041237113402</c:v>
+                  <c:v>0.41237113402061853</c:v>
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>0.41836734693877553</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.42424242424242425</c:v>
+                  <c:v>0.41414141414141414</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6470,304 +6676,304 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.37</c:v>
+                  <c:v>0.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7114,304 +7320,304 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.47</c:v>
+                  <c:v>0.45999999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7758,304 +7964,304 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
                 <c:pt idx="0">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.42</c:v>
+                  <c:v>0.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -37525,6 +37731,1676 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008B26CF-2180-45F2-BE3B-DE8DB6CBE331}">
+  <dimension ref="A1:I113"/>
+  <sheetFormatPr defaultColWidth="18.109375" defaultRowHeight="36.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.109375" style="115" customWidth="1"/>
+    <col min="2" max="2" width="24" style="112" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+    </row>
+    <row r="2" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="123" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="123" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="123" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="123" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="128"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="109"/>
+    </row>
+    <row r="3" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="130"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="H3" s="125" t="s">
+        <v>246</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="117">
+        <v>1</v>
+      </c>
+      <c r="B4" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="136">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="D4" s="136">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="E4" s="136">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="F4" s="136">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="G4" s="126"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="109"/>
+    </row>
+    <row r="5" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="117">
+        <v>2</v>
+      </c>
+      <c r="B5" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="136">
+        <v>5.5640000000000001</v>
+      </c>
+      <c r="D5" s="136">
+        <v>6.96</v>
+      </c>
+      <c r="E5" s="136">
+        <v>7.3319999999999999</v>
+      </c>
+      <c r="F5" s="136">
+        <v>9.0020000000000007</v>
+      </c>
+      <c r="G5" s="126"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="109"/>
+    </row>
+    <row r="6" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="117">
+        <v>3</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="136">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="D6" s="136">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="E6" s="136">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="F6" s="136">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="G6" s="126"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="109"/>
+    </row>
+    <row r="7" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="117">
+        <v>4</v>
+      </c>
+      <c r="B7" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="136">
+        <v>0.35842535614937099</v>
+      </c>
+      <c r="D7" s="136">
+        <v>0.281035047494268</v>
+      </c>
+      <c r="E7" s="136">
+        <v>0.13856023996000599</v>
+      </c>
+      <c r="F7" s="136">
+        <v>0.109410801963993</v>
+      </c>
+      <c r="G7" s="126"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="109"/>
+    </row>
+    <row r="8" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="117">
+        <v>5</v>
+      </c>
+      <c r="B8" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="136">
+        <v>0.55685745595549196</v>
+      </c>
+      <c r="D8" s="136">
+        <v>0.63216508352440204</v>
+      </c>
+      <c r="E8" s="136">
+        <v>0.82661223129478401</v>
+      </c>
+      <c r="F8" s="136">
+        <v>0.87283142389525303</v>
+      </c>
+      <c r="G8" s="126"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="109"/>
+    </row>
+    <row r="9" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="117">
+        <v>6</v>
+      </c>
+      <c r="B9" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="136">
+        <v>1.4721402680603499</v>
+      </c>
+      <c r="D9" s="136">
+        <v>1.5453652145430701</v>
+      </c>
+      <c r="E9" s="136">
+        <v>1.7917847025495699</v>
+      </c>
+      <c r="F9" s="136">
+        <v>1.8550736497545</v>
+      </c>
+      <c r="G9" s="126"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="109"/>
+    </row>
+    <row r="10" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="117">
+        <v>7</v>
+      </c>
+      <c r="B10" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="136">
+        <v>0.32597150805024</v>
+      </c>
+      <c r="D10" s="136">
+        <v>0.30306256141500099</v>
+      </c>
+      <c r="E10" s="136">
+        <v>7.5237460423262403E-2</v>
+      </c>
+      <c r="F10" s="136">
+        <v>6.1211129296235497E-2</v>
+      </c>
+      <c r="G10" s="126"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="109"/>
+    </row>
+    <row r="11" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="117">
+        <v>8</v>
+      </c>
+      <c r="B11" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="136">
+        <v>0.201888223889404</v>
+      </c>
+      <c r="D11" s="136">
+        <v>0.151572224041925</v>
+      </c>
+      <c r="E11" s="136">
+        <v>0.13297783702716201</v>
+      </c>
+      <c r="F11" s="136">
+        <v>8.3715220949263397E-2</v>
+      </c>
+      <c r="G11" s="126"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="109"/>
+    </row>
+    <row r="12" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="117">
+        <v>9</v>
+      </c>
+      <c r="B12" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="136">
+        <v>0.201888223889404</v>
+      </c>
+      <c r="D12" s="136">
+        <v>0.151572224041925</v>
+      </c>
+      <c r="E12" s="136">
+        <v>0.13297783702716201</v>
+      </c>
+      <c r="F12" s="136">
+        <v>8.3715220949263397E-2</v>
+      </c>
+      <c r="G12" s="126"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="109"/>
+    </row>
+    <row r="13" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="117">
+        <v>10</v>
+      </c>
+      <c r="B13" s="114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="136">
+        <v>1</v>
+      </c>
+      <c r="D13" s="136">
+        <v>0.65348619560131005</v>
+      </c>
+      <c r="E13" s="136">
+        <v>0.37337314346960598</v>
+      </c>
+      <c r="F13" s="136">
+        <v>0.30808002481389501</v>
+      </c>
+      <c r="G13" s="126"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="109"/>
+    </row>
+    <row r="14" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="117">
+        <v>11</v>
+      </c>
+      <c r="B14" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" s="136">
+        <v>0</v>
+      </c>
+      <c r="D14" s="136">
+        <v>0.34651380439868901</v>
+      </c>
+      <c r="E14" s="136">
+        <v>0.27530240391976601</v>
+      </c>
+      <c r="F14" s="136">
+        <v>0.21789702233250599</v>
+      </c>
+      <c r="G14" s="126"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="109"/>
+    </row>
+    <row r="15" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="117">
+        <v>12</v>
+      </c>
+      <c r="B15" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="136">
+        <v>0</v>
+      </c>
+      <c r="D15" s="136">
+        <v>0</v>
+      </c>
+      <c r="E15" s="136">
+        <v>0</v>
+      </c>
+      <c r="F15" s="136">
+        <v>0.249379652605459</v>
+      </c>
+      <c r="G15" s="126"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="109"/>
+    </row>
+    <row r="16" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="117">
+        <v>13</v>
+      </c>
+      <c r="B16" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="136">
+        <v>0</v>
+      </c>
+      <c r="D16" s="136">
+        <v>0</v>
+      </c>
+      <c r="E16" s="136">
+        <v>0.351324452610626</v>
+      </c>
+      <c r="F16" s="136">
+        <v>0.224643300248138</v>
+      </c>
+      <c r="G16" s="126"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="109"/>
+    </row>
+    <row r="17" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="117">
+        <v>14</v>
+      </c>
+      <c r="B17" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="136">
+        <v>0</v>
+      </c>
+      <c r="D17" s="136">
+        <v>0.34651380439868901</v>
+      </c>
+      <c r="E17" s="136">
+        <v>0.97795130914102002</v>
+      </c>
+      <c r="F17" s="136">
+        <v>1.3905862282878401</v>
+      </c>
+      <c r="G17" s="126"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="109"/>
+    </row>
+    <row r="18" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="117">
+        <v>15</v>
+      </c>
+      <c r="B18" s="134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="136">
+        <v>0</v>
+      </c>
+      <c r="D18" s="136">
+        <v>3.3156716417910397E-2</v>
+      </c>
+      <c r="E18" s="136">
+        <v>6.1082089552238802E-2</v>
+      </c>
+      <c r="F18" s="136">
+        <v>6.6589552238805902E-2</v>
+      </c>
+      <c r="G18" s="126"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="109"/>
+    </row>
+    <row r="19" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="117">
+        <v>16</v>
+      </c>
+      <c r="B19" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="136">
+        <v>0.16205970149253701</v>
+      </c>
+      <c r="D19" s="136">
+        <v>0.13120000000000001</v>
+      </c>
+      <c r="E19" s="136">
+        <v>0.128711111111111</v>
+      </c>
+      <c r="F19" s="136">
+        <v>0.109118181818181</v>
+      </c>
+      <c r="G19" s="126"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+    </row>
+    <row r="20" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="117">
+        <v>17</v>
+      </c>
+      <c r="B20" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" s="136">
+        <v>0.16205970149253701</v>
+      </c>
+      <c r="D20" s="136">
+        <v>0.16435671641791</v>
+      </c>
+      <c r="E20" s="136">
+        <v>0.18979320066334901</v>
+      </c>
+      <c r="F20" s="136">
+        <v>0.175707734056987</v>
+      </c>
+      <c r="G20" s="126"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+    </row>
+    <row r="21" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="135">
+        <v>18</v>
+      </c>
+      <c r="B21" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C21" s="136">
+        <v>1.42397931945263</v>
+      </c>
+      <c r="D21" s="136">
+        <v>1.9416966917785701</v>
+      </c>
+      <c r="E21" s="136">
+        <v>2.8889074043214999</v>
+      </c>
+      <c r="F21" s="136">
+        <v>3.2820512820512802</v>
+      </c>
+      <c r="G21" s="126"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+    </row>
+    <row r="22" spans="1:9" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+    </row>
+    <row r="23" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+    </row>
+    <row r="24" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" s="120" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" s="120"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+    </row>
+    <row r="25" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="123" t="s">
+        <v>220</v>
+      </c>
+      <c r="D25" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="127"/>
+      <c r="F25" s="109"/>
+    </row>
+    <row r="26" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B26" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="125" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="117">
+        <v>1</v>
+      </c>
+      <c r="B27" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="136">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="D27" s="126"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="109"/>
+    </row>
+    <row r="28" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="117">
+        <v>2</v>
+      </c>
+      <c r="B28" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" s="136">
+        <v>5.5640000000000001</v>
+      </c>
+      <c r="D28" s="126"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="109"/>
+    </row>
+    <row r="29" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="117">
+        <v>3</v>
+      </c>
+      <c r="B29" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C29" s="136">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="D29" s="126"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="109"/>
+    </row>
+    <row r="30" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="117">
+        <v>4</v>
+      </c>
+      <c r="B30" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="136">
+        <v>0.35842535614937099</v>
+      </c>
+      <c r="D30" s="126"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="109"/>
+    </row>
+    <row r="31" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="117">
+        <v>5</v>
+      </c>
+      <c r="B31" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="136">
+        <v>0.55685745595549196</v>
+      </c>
+      <c r="D31" s="126"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="109"/>
+    </row>
+    <row r="32" spans="1:9" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="117">
+        <v>6</v>
+      </c>
+      <c r="B32" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="136">
+        <v>1.4721402680603499</v>
+      </c>
+      <c r="D32" s="126"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="109"/>
+    </row>
+    <row r="33" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="117">
+        <v>7</v>
+      </c>
+      <c r="B33" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" s="136">
+        <v>0.32597150805024</v>
+      </c>
+      <c r="D33" s="126"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="109"/>
+    </row>
+    <row r="34" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="117">
+        <v>8</v>
+      </c>
+      <c r="B34" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="136">
+        <v>0.201888223889404</v>
+      </c>
+      <c r="D34" s="126"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="109"/>
+    </row>
+    <row r="35" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="117">
+        <v>9</v>
+      </c>
+      <c r="B35" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C35" s="136">
+        <v>0.201888223889404</v>
+      </c>
+      <c r="D35" s="126"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="109"/>
+    </row>
+    <row r="36" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="117">
+        <v>10</v>
+      </c>
+      <c r="B36" s="114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="136">
+        <v>1</v>
+      </c>
+      <c r="D36" s="126"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="109"/>
+    </row>
+    <row r="37" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="117">
+        <v>11</v>
+      </c>
+      <c r="B37" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" s="136">
+        <v>0</v>
+      </c>
+      <c r="D37" s="126"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="109"/>
+    </row>
+    <row r="38" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="117">
+        <v>12</v>
+      </c>
+      <c r="B38" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="136">
+        <v>0</v>
+      </c>
+      <c r="D38" s="126"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="109"/>
+    </row>
+    <row r="39" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="117">
+        <v>13</v>
+      </c>
+      <c r="B39" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="136">
+        <v>0</v>
+      </c>
+      <c r="D39" s="126"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="109"/>
+    </row>
+    <row r="40" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="117">
+        <v>14</v>
+      </c>
+      <c r="B40" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="136">
+        <v>0</v>
+      </c>
+      <c r="D40" s="126"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="109"/>
+    </row>
+    <row r="41" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="117">
+        <v>15</v>
+      </c>
+      <c r="B41" s="134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="136">
+        <v>0</v>
+      </c>
+      <c r="D41" s="126"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="109"/>
+    </row>
+    <row r="42" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="117">
+        <v>16</v>
+      </c>
+      <c r="B42" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="C42" s="136">
+        <v>0.16205970149253701</v>
+      </c>
+      <c r="D42" s="126"/>
+      <c r="E42" s="109"/>
+      <c r="F42" s="109"/>
+    </row>
+    <row r="43" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="117">
+        <v>17</v>
+      </c>
+      <c r="B43" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C43" s="136">
+        <v>0.16205970149253701</v>
+      </c>
+      <c r="D43" s="126"/>
+      <c r="E43" s="109"/>
+      <c r="F43" s="109"/>
+    </row>
+    <row r="44" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="135">
+        <v>18</v>
+      </c>
+      <c r="B44" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" s="136">
+        <v>1.42397931945263</v>
+      </c>
+      <c r="D44" s="126"/>
+      <c r="E44" s="109"/>
+      <c r="F44" s="109"/>
+    </row>
+    <row r="46" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C47" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" s="120" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="120"/>
+      <c r="F47" s="121"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="111"/>
+    </row>
+    <row r="48" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C48" s="123" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="127"/>
+      <c r="F48" s="109"/>
+    </row>
+    <row r="49" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D49" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="125" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="117">
+        <v>1</v>
+      </c>
+      <c r="B50" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" s="136">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="D50" s="126"/>
+      <c r="E50" s="124"/>
+      <c r="F50" s="109"/>
+    </row>
+    <row r="51" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="117">
+        <v>2</v>
+      </c>
+      <c r="B51" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="C51" s="136">
+        <v>6.96</v>
+      </c>
+      <c r="D51" s="126"/>
+      <c r="E51" s="124"/>
+      <c r="F51" s="109"/>
+    </row>
+    <row r="52" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="117">
+        <v>3</v>
+      </c>
+      <c r="B52" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="136">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="D52" s="126"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="109"/>
+    </row>
+    <row r="53" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="117">
+        <v>4</v>
+      </c>
+      <c r="B53" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C53" s="136">
+        <v>0.281035047494268</v>
+      </c>
+      <c r="D53" s="126"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="109"/>
+    </row>
+    <row r="54" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="117">
+        <v>5</v>
+      </c>
+      <c r="B54" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="136">
+        <v>0.63216508352440204</v>
+      </c>
+      <c r="D54" s="126"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="109"/>
+    </row>
+    <row r="55" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="117">
+        <v>6</v>
+      </c>
+      <c r="B55" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="C55" s="136">
+        <v>1.5453652145430701</v>
+      </c>
+      <c r="D55" s="126"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="109"/>
+    </row>
+    <row r="56" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="117">
+        <v>7</v>
+      </c>
+      <c r="B56" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" s="136">
+        <v>0.30306256141500099</v>
+      </c>
+      <c r="D56" s="126"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="109"/>
+    </row>
+    <row r="57" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="117">
+        <v>8</v>
+      </c>
+      <c r="B57" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="C57" s="136">
+        <v>0.151572224041925</v>
+      </c>
+      <c r="D57" s="126"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="109"/>
+    </row>
+    <row r="58" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="117">
+        <v>9</v>
+      </c>
+      <c r="B58" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="136">
+        <v>0.151572224041925</v>
+      </c>
+      <c r="D58" s="126"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="109"/>
+    </row>
+    <row r="59" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="117">
+        <v>10</v>
+      </c>
+      <c r="B59" s="114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="136">
+        <v>0.65348619560131005</v>
+      </c>
+      <c r="D59" s="126"/>
+      <c r="E59" s="124"/>
+      <c r="F59" s="109"/>
+    </row>
+    <row r="60" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="117">
+        <v>11</v>
+      </c>
+      <c r="B60" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="136">
+        <v>0.34651380439868901</v>
+      </c>
+      <c r="D60" s="126"/>
+      <c r="E60" s="124"/>
+      <c r="F60" s="109"/>
+    </row>
+    <row r="61" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="117">
+        <v>12</v>
+      </c>
+      <c r="B61" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C61" s="136">
+        <v>0</v>
+      </c>
+      <c r="D61" s="126"/>
+      <c r="E61" s="124"/>
+      <c r="F61" s="109"/>
+    </row>
+    <row r="62" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="117">
+        <v>13</v>
+      </c>
+      <c r="B62" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="C62" s="136">
+        <v>0</v>
+      </c>
+      <c r="D62" s="126"/>
+      <c r="E62" s="124"/>
+      <c r="F62" s="109"/>
+    </row>
+    <row r="63" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="117">
+        <v>14</v>
+      </c>
+      <c r="B63" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C63" s="136">
+        <v>0.34651380439868901</v>
+      </c>
+      <c r="D63" s="126"/>
+      <c r="E63" s="124"/>
+      <c r="F63" s="109"/>
+    </row>
+    <row r="64" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="117">
+        <v>15</v>
+      </c>
+      <c r="B64" s="134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C64" s="136">
+        <v>3.3156716417910397E-2</v>
+      </c>
+      <c r="D64" s="126"/>
+      <c r="E64" s="124"/>
+      <c r="F64" s="109"/>
+    </row>
+    <row r="65" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="117">
+        <v>16</v>
+      </c>
+      <c r="B65" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="C65" s="136">
+        <v>0.13120000000000001</v>
+      </c>
+      <c r="D65" s="126"/>
+      <c r="E65" s="109"/>
+      <c r="F65" s="109"/>
+    </row>
+    <row r="66" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="117">
+        <v>17</v>
+      </c>
+      <c r="B66" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" s="136">
+        <v>0.16435671641791</v>
+      </c>
+      <c r="D66" s="126"/>
+      <c r="E66" s="109"/>
+      <c r="F66" s="109"/>
+    </row>
+    <row r="67" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="135">
+        <v>18</v>
+      </c>
+      <c r="B67" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C67" s="136">
+        <v>1.9416966917785701</v>
+      </c>
+      <c r="D67" s="126"/>
+      <c r="E67" s="109"/>
+      <c r="F67" s="109"/>
+    </row>
+    <row r="69" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C70" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" s="120" t="s">
+        <v>250</v>
+      </c>
+      <c r="E70" s="120"/>
+      <c r="F70" s="121"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+    </row>
+    <row r="71" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C71" s="123" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" s="127"/>
+      <c r="F71" s="109"/>
+    </row>
+    <row r="72" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C72" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D72" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="E72" s="125" t="s">
+        <v>246</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="117">
+        <v>1</v>
+      </c>
+      <c r="B73" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C73" s="136">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="D73" s="126"/>
+      <c r="E73" s="124"/>
+      <c r="F73" s="109"/>
+    </row>
+    <row r="74" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="117">
+        <v>2</v>
+      </c>
+      <c r="B74" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="C74" s="136">
+        <v>7.3319999999999999</v>
+      </c>
+      <c r="D74" s="126"/>
+      <c r="E74" s="124"/>
+      <c r="F74" s="109"/>
+    </row>
+    <row r="75" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="117">
+        <v>3</v>
+      </c>
+      <c r="B75" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="136">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="D75" s="126"/>
+      <c r="E75" s="124"/>
+      <c r="F75" s="109"/>
+    </row>
+    <row r="76" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="117">
+        <v>4</v>
+      </c>
+      <c r="B76" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" s="136">
+        <v>0.13856023996000599</v>
+      </c>
+      <c r="D76" s="126"/>
+      <c r="E76" s="124"/>
+      <c r="F76" s="109"/>
+    </row>
+    <row r="77" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="117">
+        <v>5</v>
+      </c>
+      <c r="B77" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77" s="136">
+        <v>0.82661223129478401</v>
+      </c>
+      <c r="D77" s="126"/>
+      <c r="E77" s="124"/>
+      <c r="F77" s="109"/>
+    </row>
+    <row r="78" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="117">
+        <v>6</v>
+      </c>
+      <c r="B78" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78" s="136">
+        <v>1.7917847025495699</v>
+      </c>
+      <c r="D78" s="126"/>
+      <c r="E78" s="124"/>
+      <c r="F78" s="109"/>
+    </row>
+    <row r="79" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="117">
+        <v>7</v>
+      </c>
+      <c r="B79" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C79" s="136">
+        <v>7.5237460423262403E-2</v>
+      </c>
+      <c r="D79" s="126"/>
+      <c r="E79" s="124"/>
+      <c r="F79" s="109"/>
+    </row>
+    <row r="80" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="117">
+        <v>8</v>
+      </c>
+      <c r="B80" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="C80" s="136">
+        <v>0.13297783702716201</v>
+      </c>
+      <c r="D80" s="126"/>
+      <c r="E80" s="124"/>
+      <c r="F80" s="109"/>
+    </row>
+    <row r="81" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="117">
+        <v>9</v>
+      </c>
+      <c r="B81" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="136">
+        <v>0.13297783702716201</v>
+      </c>
+      <c r="D81" s="126"/>
+      <c r="E81" s="124"/>
+      <c r="F81" s="109"/>
+    </row>
+    <row r="82" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="117">
+        <v>10</v>
+      </c>
+      <c r="B82" s="114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C82" s="136">
+        <v>0.37337314346960598</v>
+      </c>
+      <c r="D82" s="126"/>
+      <c r="E82" s="124"/>
+      <c r="F82" s="109"/>
+    </row>
+    <row r="83" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="117">
+        <v>11</v>
+      </c>
+      <c r="B83" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C83" s="136">
+        <v>0.27530240391976601</v>
+      </c>
+      <c r="D83" s="126"/>
+      <c r="E83" s="124"/>
+      <c r="F83" s="109"/>
+    </row>
+    <row r="84" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="117">
+        <v>12</v>
+      </c>
+      <c r="B84" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C84" s="136">
+        <v>0</v>
+      </c>
+      <c r="D84" s="126"/>
+      <c r="E84" s="124"/>
+      <c r="F84" s="109"/>
+    </row>
+    <row r="85" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="117">
+        <v>13</v>
+      </c>
+      <c r="B85" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="C85" s="136">
+        <v>0.351324452610626</v>
+      </c>
+      <c r="D85" s="126"/>
+      <c r="E85" s="124"/>
+      <c r="F85" s="109"/>
+    </row>
+    <row r="86" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="117">
+        <v>14</v>
+      </c>
+      <c r="B86" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" s="136">
+        <v>0.97795130914102002</v>
+      </c>
+      <c r="D86" s="126"/>
+      <c r="E86" s="124"/>
+      <c r="F86" s="109"/>
+    </row>
+    <row r="87" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="117">
+        <v>15</v>
+      </c>
+      <c r="B87" s="134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C87" s="136">
+        <v>6.1082089552238802E-2</v>
+      </c>
+      <c r="D87" s="126"/>
+      <c r="E87" s="124"/>
+      <c r="F87" s="109"/>
+    </row>
+    <row r="88" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="117">
+        <v>16</v>
+      </c>
+      <c r="B88" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="C88" s="136">
+        <v>0.128711111111111</v>
+      </c>
+      <c r="D88" s="126"/>
+      <c r="E88" s="109"/>
+      <c r="F88" s="109"/>
+    </row>
+    <row r="89" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="117">
+        <v>17</v>
+      </c>
+      <c r="B89" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" s="136">
+        <v>0.18979320066334901</v>
+      </c>
+      <c r="D89" s="126"/>
+      <c r="E89" s="109"/>
+      <c r="F89" s="109"/>
+    </row>
+    <row r="90" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="135">
+        <v>18</v>
+      </c>
+      <c r="B90" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="136">
+        <v>2.8889074043214999</v>
+      </c>
+      <c r="D90" s="126"/>
+      <c r="E90" s="109"/>
+      <c r="F90" s="109"/>
+    </row>
+    <row r="92" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="93" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C93" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="E93" s="120"/>
+      <c r="F93" s="121"/>
+      <c r="G93" s="111"/>
+      <c r="H93" s="111"/>
+    </row>
+    <row r="94" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C94" s="123" t="s">
+        <v>223</v>
+      </c>
+      <c r="D94" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E94" s="127"/>
+      <c r="F94" s="109"/>
+    </row>
+    <row r="95" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="132" t="s">
+        <v>224</v>
+      </c>
+      <c r="B95" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D95" s="125" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" s="125" t="s">
+        <v>246</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="117">
+        <v>1</v>
+      </c>
+      <c r="B96" s="113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C96" s="136">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="D96" s="126"/>
+      <c r="E96" s="124"/>
+      <c r="F96" s="109"/>
+    </row>
+    <row r="97" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="117">
+        <v>2</v>
+      </c>
+      <c r="B97" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="C97" s="136">
+        <v>9.0020000000000007</v>
+      </c>
+      <c r="D97" s="126"/>
+      <c r="E97" s="124"/>
+      <c r="F97" s="109"/>
+    </row>
+    <row r="98" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="117">
+        <v>3</v>
+      </c>
+      <c r="B98" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="C98" s="136">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="D98" s="126"/>
+      <c r="E98" s="124"/>
+      <c r="F98" s="109"/>
+    </row>
+    <row r="99" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="117">
+        <v>4</v>
+      </c>
+      <c r="B99" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="C99" s="136">
+        <v>0.109410801963993</v>
+      </c>
+      <c r="D99" s="126"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="109"/>
+    </row>
+    <row r="100" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="117">
+        <v>5</v>
+      </c>
+      <c r="B100" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="C100" s="136">
+        <v>0.87283142389525303</v>
+      </c>
+      <c r="D100" s="126"/>
+      <c r="E100" s="124"/>
+      <c r="F100" s="109"/>
+    </row>
+    <row r="101" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="117">
+        <v>6</v>
+      </c>
+      <c r="B101" s="131" t="s">
+        <v>233</v>
+      </c>
+      <c r="C101" s="136">
+        <v>1.8550736497545</v>
+      </c>
+      <c r="D101" s="126"/>
+      <c r="E101" s="124"/>
+      <c r="F101" s="109"/>
+    </row>
+    <row r="102" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="117">
+        <v>7</v>
+      </c>
+      <c r="B102" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="C102" s="136">
+        <v>6.1211129296235497E-2</v>
+      </c>
+      <c r="D102" s="126"/>
+      <c r="E102" s="124"/>
+      <c r="F102" s="109"/>
+    </row>
+    <row r="103" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="117">
+        <v>8</v>
+      </c>
+      <c r="B103" s="114" t="s">
+        <v>235</v>
+      </c>
+      <c r="C103" s="136">
+        <v>8.3715220949263397E-2</v>
+      </c>
+      <c r="D103" s="126"/>
+      <c r="E103" s="124"/>
+      <c r="F103" s="109"/>
+    </row>
+    <row r="104" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="117">
+        <v>9</v>
+      </c>
+      <c r="B104" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C104" s="136">
+        <v>8.3715220949263397E-2</v>
+      </c>
+      <c r="D104" s="126"/>
+      <c r="E104" s="124"/>
+      <c r="F104" s="109"/>
+    </row>
+    <row r="105" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="117">
+        <v>10</v>
+      </c>
+      <c r="B105" s="114" t="s">
+        <v>240</v>
+      </c>
+      <c r="C105" s="136">
+        <v>0.30808002481389501</v>
+      </c>
+      <c r="D105" s="126"/>
+      <c r="E105" s="124"/>
+      <c r="F105" s="109"/>
+    </row>
+    <row r="106" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="117">
+        <v>11</v>
+      </c>
+      <c r="B106" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C106" s="136">
+        <v>0.21789702233250599</v>
+      </c>
+      <c r="D106" s="126"/>
+      <c r="E106" s="124"/>
+      <c r="F106" s="109"/>
+    </row>
+    <row r="107" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="117">
+        <v>12</v>
+      </c>
+      <c r="B107" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="136">
+        <v>0.249379652605459</v>
+      </c>
+      <c r="D107" s="126"/>
+      <c r="E107" s="124"/>
+      <c r="F107" s="109"/>
+    </row>
+    <row r="108" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="117">
+        <v>13</v>
+      </c>
+      <c r="B108" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="C108" s="136">
+        <v>0.224643300248138</v>
+      </c>
+      <c r="D108" s="126"/>
+      <c r="E108" s="124"/>
+      <c r="F108" s="109"/>
+    </row>
+    <row r="109" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="117">
+        <v>14</v>
+      </c>
+      <c r="B109" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C109" s="136">
+        <v>1.3905862282878401</v>
+      </c>
+      <c r="D109" s="126"/>
+      <c r="E109" s="124"/>
+      <c r="F109" s="109"/>
+    </row>
+    <row r="110" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="117">
+        <v>15</v>
+      </c>
+      <c r="B110" s="134" t="s">
+        <v>236</v>
+      </c>
+      <c r="C110" s="136">
+        <v>6.6589552238805902E-2</v>
+      </c>
+      <c r="D110" s="126"/>
+      <c r="E110" s="124"/>
+      <c r="F110" s="109"/>
+    </row>
+    <row r="111" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="117">
+        <v>16</v>
+      </c>
+      <c r="B111" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="C111" s="136">
+        <v>0.109118181818181</v>
+      </c>
+      <c r="D111" s="126"/>
+      <c r="E111" s="109"/>
+      <c r="F111" s="109"/>
+    </row>
+    <row r="112" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="117">
+        <v>17</v>
+      </c>
+      <c r="B112" s="134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C112" s="136">
+        <v>0.175707734056987</v>
+      </c>
+      <c r="D112" s="126"/>
+      <c r="E112" s="109"/>
+      <c r="F112" s="109"/>
+    </row>
+    <row r="113" spans="1:6" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="135">
+        <v>18</v>
+      </c>
+      <c r="B113" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" s="136">
+        <v>3.2820512820512802</v>
+      </c>
+      <c r="D113" s="126"/>
+      <c r="E113" s="109"/>
+      <c r="F113" s="109"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A862460A-081D-4C06-A176-B1459E009989}">
   <dimension ref="A1:AM35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -51504,11 +53380,11 @@
       </c>
       <c r="B1" s="68">
         <f ca="1">IF(ABS(RANDBETWEEN(0,100)-RANDBETWEEN(0,100))&lt;=25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="68">
         <f t="shared" ref="C1:BN1" ca="1" si="0">IF(ABS(RANDBETWEEN(0,100)-RANDBETWEEN(0,100))&lt;=25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51516,7 +53392,7 @@
       </c>
       <c r="E1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51544,11 +53420,11 @@
       </c>
       <c r="L1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51560,7 +53436,7 @@
       </c>
       <c r="P1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51568,11 +53444,11 @@
       </c>
       <c r="R1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51580,11 +53456,11 @@
       </c>
       <c r="U1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51592,15 +53468,15 @@
       </c>
       <c r="X1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51608,19 +53484,19 @@
       </c>
       <c r="AB1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51628,11 +53504,11 @@
       </c>
       <c r="AG1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51644,7 +53520,7 @@
       </c>
       <c r="AK1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51652,7 +53528,7 @@
       </c>
       <c r="AM1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51668,11 +53544,11 @@
       </c>
       <c r="AQ1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51684,7 +53560,7 @@
       </c>
       <c r="AU1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51692,11 +53568,11 @@
       </c>
       <c r="AW1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51708,7 +53584,7 @@
       </c>
       <c r="BA1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51732,11 +53608,11 @@
       </c>
       <c r="BG1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51744,7 +53620,7 @@
       </c>
       <c r="BJ1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51752,11 +53628,11 @@
       </c>
       <c r="BL1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM1" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN1" s="68">
         <f t="shared" ca="1" si="0"/>
@@ -51764,7 +53640,7 @@
       </c>
       <c r="BO1" s="68">
         <f t="shared" ref="BO1:CW1" ca="1" si="1">IF(ABS(RANDBETWEEN(0,100)-RANDBETWEEN(0,100))&lt;=25,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51772,7 +53648,7 @@
       </c>
       <c r="BQ1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51780,15 +53656,15 @@
       </c>
       <c r="BS1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51800,7 +53676,7 @@
       </c>
       <c r="BX1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51808,7 +53684,7 @@
       </c>
       <c r="BZ1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51820,19 +53696,19 @@
       </c>
       <c r="CC1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51840,51 +53716,51 @@
       </c>
       <c r="CH1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CS1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51892,11 +53768,11 @@
       </c>
       <c r="CU1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV1" s="68">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW1" s="68">
         <f t="shared" ca="1" si="1"/>
@@ -51909,107 +53785,107 @@
       </c>
       <c r="B2" s="68">
         <f ca="1">SUM($B$1:B1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="68">
         <f ca="1">SUM($B$1:C1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="68">
         <f ca="1">SUM($B$1:D1)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="68">
         <f ca="1">SUM($B$1:E1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="68">
         <f ca="1">SUM($B$1:F1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="68">
         <f ca="1">SUM($B$1:G1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="68">
         <f ca="1">SUM($B$1:H1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="68">
         <f ca="1">SUM($B$1:I1)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" s="68">
         <f ca="1">SUM($B$1:J1)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="68">
         <f ca="1">SUM($B$1:K1)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" s="68">
         <f ca="1">SUM($B$1:L1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="68">
         <f ca="1">SUM($B$1:M1)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N2" s="68">
         <f ca="1">SUM($B$1:N1)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O2" s="68">
         <f ca="1">SUM($B$1:O1)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P2" s="68">
         <f ca="1">SUM($B$1:P1)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="68">
         <f ca="1">SUM($B$1:Q1)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R2" s="68">
         <f ca="1">SUM($B$1:R1)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S2" s="68">
         <f ca="1">SUM($B$1:S1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T2" s="68">
         <f ca="1">SUM($B$1:T1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U2" s="68">
         <f ca="1">SUM($B$1:U1)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V2" s="68">
         <f ca="1">SUM($B$1:V1)</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W2" s="68">
         <f ca="1">SUM($B$1:W1)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X2" s="68">
         <f ca="1">SUM($B$1:X1)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y2" s="68">
         <f ca="1">SUM($B$1:Y1)</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="68">
         <f ca="1">SUM($B$1:Z1)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA2" s="68">
         <f ca="1">SUM($B$1:AA1)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB2" s="68">
         <f ca="1">SUM($B$1:AB1)</f>
@@ -52017,211 +53893,211 @@
       </c>
       <c r="AC2" s="68">
         <f ca="1">SUM($B$1:AC1)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD2" s="68">
         <f ca="1">SUM($B$1:AD1)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE2" s="68">
         <f ca="1">SUM($B$1:AE1)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AF2" s="68">
         <f ca="1">SUM($B$1:AF1)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG2" s="68">
         <f ca="1">SUM($B$1:AG1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH2" s="68">
         <f ca="1">SUM($B$1:AH1)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI2" s="68">
         <f ca="1">SUM($B$1:AI1)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AJ2" s="68">
         <f ca="1">SUM($B$1:AJ1)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK2" s="68">
         <f ca="1">SUM($B$1:AK1)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL2" s="68">
         <f ca="1">SUM($B$1:AL1)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM2" s="68">
         <f ca="1">SUM($B$1:AM1)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AN2" s="68">
         <f ca="1">SUM($B$1:AN1)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO2" s="68">
         <f ca="1">SUM($B$1:AO1)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AP2" s="68">
         <f ca="1">SUM($B$1:AP1)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ2" s="68">
         <f ca="1">SUM($B$1:AQ1)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AR2" s="68">
         <f ca="1">SUM($B$1:AR1)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AS2" s="68">
         <f ca="1">SUM($B$1:AS1)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AT2" s="68">
         <f ca="1">SUM($B$1:AT1)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AU2" s="68">
         <f ca="1">SUM($B$1:AU1)</f>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AV2" s="68">
         <f ca="1">SUM($B$1:AV1)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AW2" s="68">
         <f ca="1">SUM($B$1:AW1)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AX2" s="68">
         <f ca="1">SUM($B$1:AX1)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AY2" s="68">
         <f ca="1">SUM($B$1:AY1)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AZ2" s="68">
         <f ca="1">SUM($B$1:AZ1)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BA2" s="68">
         <f ca="1">SUM($B$1:BA1)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB2" s="68">
         <f ca="1">SUM($B$1:BB1)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BC2" s="68">
         <f ca="1">SUM($B$1:BC1)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD2" s="68">
         <f ca="1">SUM($B$1:BD1)</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE2" s="68">
         <f ca="1">SUM($B$1:BE1)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BF2" s="68">
         <f ca="1">SUM($B$1:BF1)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BG2" s="68">
         <f ca="1">SUM($B$1:BG1)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BH2" s="68">
         <f ca="1">SUM($B$1:BH1)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BI2" s="68">
         <f ca="1">SUM($B$1:BI1)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BJ2" s="68">
         <f ca="1">SUM($B$1:BJ1)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BK2" s="68">
         <f ca="1">SUM($B$1:BK1)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BL2" s="68">
         <f ca="1">SUM($B$1:BL1)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BM2" s="68">
         <f ca="1">SUM($B$1:BM1)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BN2" s="68">
         <f ca="1">SUM($B$1:BN1)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BO2" s="68">
         <f ca="1">SUM($B$1:BO1)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="BP2" s="68">
         <f ca="1">SUM($B$1:BP1)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="BQ2" s="68">
         <f ca="1">SUM($B$1:BQ1)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BR2" s="68">
         <f ca="1">SUM($B$1:BR1)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BS2" s="68">
         <f ca="1">SUM($B$1:BS1)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BT2" s="68">
         <f ca="1">SUM($B$1:BT1)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BU2" s="68">
         <f ca="1">SUM($B$1:BU1)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BV2" s="68">
         <f ca="1">SUM($B$1:BV1)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW2" s="68">
         <f ca="1">SUM($B$1:BW1)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="BX2" s="68">
         <f ca="1">SUM($B$1:BX1)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BY2" s="68">
         <f ca="1">SUM($B$1:BY1)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BZ2" s="68">
         <f ca="1">SUM($B$1:BZ1)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA2" s="68">
         <f ca="1">SUM($B$1:CA1)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB2" s="68">
         <f ca="1">SUM($B$1:CB1)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC2" s="68">
         <f ca="1">SUM($B$1:CC1)</f>
@@ -52229,7 +54105,7 @@
       </c>
       <c r="CD2" s="68">
         <f ca="1">SUM($B$1:CD1)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CE2" s="68">
         <f ca="1">SUM($B$1:CE1)</f>
@@ -52237,11 +54113,11 @@
       </c>
       <c r="CF2" s="68">
         <f ca="1">SUM($B$1:CF1)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CG2" s="68">
         <f ca="1">SUM($B$1:CG1)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CH2" s="68">
         <f ca="1">SUM($B$1:CH1)</f>
@@ -52249,7 +54125,7 @@
       </c>
       <c r="CI2" s="68">
         <f ca="1">SUM($B$1:CI1)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CJ2" s="68">
         <f ca="1">SUM($B$1:CJ1)</f>
@@ -52257,7 +54133,7 @@
       </c>
       <c r="CK2" s="68">
         <f ca="1">SUM($B$1:CK1)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CL2" s="68">
         <f ca="1">SUM($B$1:CL1)</f>
@@ -52265,15 +54141,15 @@
       </c>
       <c r="CM2" s="68">
         <f ca="1">SUM($B$1:CM1)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CN2" s="68">
         <f ca="1">SUM($B$1:CN1)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="CO2" s="68">
         <f ca="1">SUM($B$1:CO1)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CP2" s="68">
         <f ca="1">SUM($B$1:CP1)</f>
@@ -52281,7 +54157,7 @@
       </c>
       <c r="CQ2" s="68">
         <f ca="1">SUM($B$1:CQ1)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CR2" s="68">
         <f ca="1">SUM($B$1:CR1)</f>
@@ -52289,11 +54165,11 @@
       </c>
       <c r="CS2" s="68">
         <f ca="1">SUM($B$1:CS1)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="CT2" s="68">
         <f ca="1">SUM($B$1:CT1)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="CU2" s="68">
         <f ca="1">SUM($B$1:CU1)</f>
@@ -52301,11 +54177,11 @@
       </c>
       <c r="CV2" s="68">
         <f ca="1">SUM($B$1:CV1)</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW2" s="68">
         <f ca="1">SUM($B$1:CW1)</f>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:101" s="68" customFormat="1" x14ac:dyDescent="0.3">
@@ -52719,107 +54595,107 @@
       </c>
       <c r="B4" s="68">
         <f ca="1">B2/B3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="68">
         <f ca="1">C2/C3</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="68">
         <f t="shared" ref="D4:BK4" ca="1" si="40">D2/D3</f>
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="J4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.44444444444444442</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.54545454545454541</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="M4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.58333333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.61538461538461542</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="O4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.6428571428571429</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="P4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.66666666666666663</v>
+        <v>0.4</v>
       </c>
       <c r="Q4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="R4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.6470588235294118</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="S4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.66666666666666663</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="T4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.63157894736842102</v>
+        <v>0.42105263157894735</v>
       </c>
       <c r="U4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="V4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.61904761904761907</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="W4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.63636363636363635</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="X4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.60869565217391308</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="Y4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.58333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="Z4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.56000000000000005</v>
+        <v>0.52</v>
       </c>
       <c r="AA4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.53846153846153844</v>
+        <v>0.5</v>
       </c>
       <c r="AB4" s="68">
         <f t="shared" ca="1" si="40"/>
@@ -52827,211 +54703,211 @@
       </c>
       <c r="AC4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.5</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="AD4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.48275862068965519</v>
+        <v>0.55172413793103448</v>
       </c>
       <c r="AE4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.46666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="AF4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.4838709677419355</v>
+        <v>0.58064516129032262</v>
       </c>
       <c r="AG4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="AH4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.48484848484848486</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="AI4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.47058823529411764</v>
+        <v>0.55882352941176472</v>
       </c>
       <c r="AJ4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.48571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="AL4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.48648648648648651</v>
+        <v>0.54054054054054057</v>
       </c>
       <c r="AM4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.47368421052631576</v>
+        <v>0.55263157894736847</v>
       </c>
       <c r="AN4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.46153846153846156</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="AO4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.45</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="AP4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.43902439024390244</v>
+        <v>0.51219512195121952</v>
       </c>
       <c r="AQ4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.42857142857142855</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="AR4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.41860465116279072</v>
+        <v>0.53488372093023251</v>
       </c>
       <c r="AS4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.40909090909090912</v>
+        <v>0.52272727272727271</v>
       </c>
       <c r="AT4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.4</v>
+        <v>0.51111111111111107</v>
       </c>
       <c r="AU4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.39130434782608697</v>
+        <v>0.52173913043478259</v>
       </c>
       <c r="AV4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.40425531914893614</v>
+        <v>0.53191489361702127</v>
       </c>
       <c r="AW4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.39583333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="AX4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.38775510204081631</v>
+        <v>0.55102040816326525</v>
       </c>
       <c r="AY4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="AZ4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.37254901960784315</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="BA4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.38461538461538464</v>
+        <v>0.51923076923076927</v>
       </c>
       <c r="BB4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.37735849056603776</v>
+        <v>0.50943396226415094</v>
       </c>
       <c r="BC4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.3888888888888889</v>
+        <v>0.51851851851851849</v>
       </c>
       <c r="BD4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.38181818181818183</v>
+        <v>0.50909090909090904</v>
       </c>
       <c r="BE4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.39285714285714285</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="BF4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.38596491228070173</v>
+        <v>0.50877192982456143</v>
       </c>
       <c r="BG4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.39655172413793105</v>
+        <v>0.5</v>
       </c>
       <c r="BH4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.40677966101694918</v>
+        <v>0.49152542372881358</v>
       </c>
       <c r="BI4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.4</v>
+        <v>0.48333333333333334</v>
       </c>
       <c r="BJ4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.4098360655737705</v>
+        <v>0.47540983606557374</v>
       </c>
       <c r="BK4" s="68">
         <f t="shared" ca="1" si="40"/>
-        <v>0.40322580645161288</v>
+        <v>0.46774193548387094</v>
       </c>
       <c r="BL4" s="68">
         <f t="shared" ref="BL4:CC4" ca="1" si="41">BL2/BL3</f>
-        <v>0.41269841269841268</v>
+        <v>0.46031746031746029</v>
       </c>
       <c r="BM4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.40625</v>
+        <v>0.46875</v>
       </c>
       <c r="BN4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.4</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="BO4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.39393939393939392</v>
+        <v>0.46969696969696972</v>
       </c>
       <c r="BP4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.38805970149253732</v>
+        <v>0.46268656716417911</v>
       </c>
       <c r="BQ4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.39705882352941174</v>
+        <v>0.45588235294117646</v>
       </c>
       <c r="BR4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.39130434782608697</v>
+        <v>0.44927536231884058</v>
       </c>
       <c r="BS4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.4</v>
+        <v>0.44285714285714284</v>
       </c>
       <c r="BT4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.39436619718309857</v>
+        <v>0.45070422535211269</v>
       </c>
       <c r="BU4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.40277777777777779</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="BV4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.39726027397260272</v>
+        <v>0.43835616438356162</v>
       </c>
       <c r="BW4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.40540540540540543</v>
+        <v>0.44594594594594594</v>
       </c>
       <c r="BX4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.41333333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="BY4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.40789473684210525</v>
+        <v>0.43421052631578949</v>
       </c>
       <c r="BZ4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.41558441558441561</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="CA4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.41025641025641024</v>
+        <v>0.42307692307692307</v>
       </c>
       <c r="CB4" s="68">
         <f t="shared" ca="1" si="41"/>
-        <v>0.4050632911392405</v>
+        <v>0.41772151898734178</v>
       </c>
       <c r="CC4" s="68">
         <f t="shared" ca="1" si="41"/>
@@ -53039,7 +54915,7 @@
       </c>
       <c r="CD4" s="68">
         <f t="shared" ref="CD4:CW4" ca="1" si="42">CD2/CD3</f>
-        <v>0.40740740740740738</v>
+        <v>0.41975308641975306</v>
       </c>
       <c r="CE4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53047,11 +54923,11 @@
       </c>
       <c r="CF4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.42168674698795183</v>
+        <v>0.40963855421686746</v>
       </c>
       <c r="CG4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.41666666666666669</v>
+        <v>0.40476190476190477</v>
       </c>
       <c r="CH4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53059,7 +54935,7 @@
       </c>
       <c r="CI4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.41860465116279072</v>
+        <v>0.40697674418604651</v>
       </c>
       <c r="CJ4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53067,7 +54943,7 @@
       </c>
       <c r="CK4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.40909090909090912</v>
+        <v>0.42045454545454547</v>
       </c>
       <c r="CL4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53075,15 +54951,15 @@
       </c>
       <c r="CM4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.41111111111111109</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="CN4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.40659340659340659</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="CO4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.41304347826086957</v>
+        <v>0.42391304347826086</v>
       </c>
       <c r="CP4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53091,7 +54967,7 @@
       </c>
       <c r="CQ4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.41489361702127658</v>
+        <v>0.42553191489361702</v>
       </c>
       <c r="CR4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53099,11 +54975,11 @@
       </c>
       <c r="CS4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.42708333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="CT4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.42268041237113402</v>
+        <v>0.41237113402061853</v>
       </c>
       <c r="CU4" s="68">
         <f t="shared" ca="1" si="42"/>
@@ -53111,413 +54987,413 @@
       </c>
       <c r="CV4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.42424242424242425</v>
+        <v>0.41414141414141414</v>
       </c>
       <c r="CW4" s="68">
         <f t="shared" ca="1" si="42"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="5" spans="1:101" x14ac:dyDescent="0.3">
       <c r="B5">
         <f ca="1">$B$7-$A$6</f>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="C5">
         <f ca="1">$B$5</f>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="D5">
         <f t="shared" ref="D5:BO5" ca="1" si="43">$B$5</f>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="J5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="M5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="N5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="P5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Q5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="R5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="S5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="T5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="U5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="V5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="W5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="X5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Y5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Z5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AA5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AB5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AC5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AD5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AE5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AF5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AG5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AH5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AI5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AJ5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AK5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AL5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AM5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AN5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AO5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AP5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AQ5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AR5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AS5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AT5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AU5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AV5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AW5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AX5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AY5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AZ5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BA5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BB5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BC5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BD5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BE5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BF5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BG5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BH5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BI5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BJ5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BK5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BL5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BM5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BN5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BO5">
         <f t="shared" ca="1" si="43"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BP5">
         <f t="shared" ref="BP5:CW5" ca="1" si="44">$B$5</f>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BQ5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BR5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BS5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BT5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BU5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BV5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BW5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BX5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BY5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BZ5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CA5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CB5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CC5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CD5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CE5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CF5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CG5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CH5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CI5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CJ5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CK5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CL5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CM5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CN5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CO5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CP5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CQ5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CR5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CS5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CT5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CU5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CV5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="CW5">
         <f t="shared" ca="1" si="44"/>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="6" spans="1:101" x14ac:dyDescent="0.3">
@@ -53526,1483 +55402,1483 @@
       </c>
       <c r="B6">
         <f ca="1">$B$7+$A$6</f>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="C6">
         <f ca="1">$B$6</f>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:BO6" ca="1" si="45">$B$6</f>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="M6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="N6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="P6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="Q6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="R6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="S6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="T6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="U6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="V6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="W6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="X6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="Y6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="Z6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AA6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AB6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AC6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AD6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AE6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AF6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AG6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AH6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AI6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AJ6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AK6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AL6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AM6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AN6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AO6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AP6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AQ6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AR6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AS6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AT6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AU6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AV6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AW6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AX6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AY6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AZ6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BA6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BB6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BC6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BD6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BE6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BF6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BG6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BH6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BI6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BJ6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BK6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BL6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BM6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BN6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BO6">
         <f t="shared" ca="1" si="45"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BP6">
         <f t="shared" ref="BP6:CW6" ca="1" si="46">$B$6</f>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BQ6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BR6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BS6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BT6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BU6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BV6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BW6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BX6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BY6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BZ6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CA6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CB6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CC6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CD6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CE6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CF6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CG6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CH6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CI6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CJ6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CK6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CL6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CM6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CN6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CO6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CP6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CQ6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CR6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CS6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CT6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CU6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CV6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="CW6">
         <f t="shared" ca="1" si="46"/>
-        <v>0.47</v>
+        <v>0.45999999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:101" x14ac:dyDescent="0.3">
       <c r="B7">
         <f ca="1">CW4</f>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="C7">
         <f ca="1">$B$7</f>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="D7">
         <f t="shared" ref="D7:BO7" ca="1" si="47">$B$7</f>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="M7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="N7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="P7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="Q7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="R7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="S7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="T7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="U7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="V7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="W7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="X7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="Y7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="Z7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AA7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AB7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AC7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AD7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AE7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AF7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AG7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AH7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AI7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AJ7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AK7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AL7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AM7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AN7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AO7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AP7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AQ7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AR7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AS7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AT7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AU7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AV7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AW7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AX7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AY7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AZ7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BA7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BB7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BC7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BD7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BE7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BF7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BG7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BH7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BI7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BJ7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BK7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BM7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BO7">
         <f t="shared" ca="1" si="47"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BP7">
         <f t="shared" ref="BP7:CW7" ca="1" si="48">$B$7</f>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BQ7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BR7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BS7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BT7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BU7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BV7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BW7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BX7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BY7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BZ7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CA7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CB7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CC7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CD7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CE7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CF7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CG7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CH7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CI7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CJ7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CK7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CL7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CM7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CN7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CO7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CP7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CQ7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CR7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CS7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CT7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CU7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CV7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CW7">
         <f t="shared" ca="1" si="48"/>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="8" spans="1:101" x14ac:dyDescent="0.3">
       <c r="B8" s="68">
         <f ca="1">SUM($B$9:B9)/B3</f>
-        <v>0.875</v>
+        <v>0.1875</v>
       </c>
       <c r="C8" s="68">
         <f ca="1">SUM($B$9:C9)/C3</f>
-        <v>0.8125</v>
+        <v>0.28125</v>
       </c>
       <c r="D8" s="68">
         <f ca="1">SUM($B$9:D9)/D3</f>
-        <v>0.7109375</v>
+        <v>0.44010416666666669</v>
       </c>
       <c r="E8" s="68">
         <f ca="1">SUM($B$9:E9)/E3</f>
-        <v>0.5390625</v>
+        <v>0.4609375</v>
       </c>
       <c r="F8" s="68">
         <f ca="1">SUM($B$9:F9)/F3</f>
-        <v>0.44218750000000001</v>
+        <v>0.37812499999999999</v>
       </c>
       <c r="G8" s="68">
         <f ca="1">SUM($B$9:G9)/G3</f>
-        <v>0.38802083333333331</v>
+        <v>0.33072916666666669</v>
       </c>
       <c r="H8" s="68">
         <f ca="1">SUM($B$9:H9)/H3</f>
-        <v>0.3671875</v>
+        <v>0.31138392857142855</v>
       </c>
       <c r="I8" s="68">
         <f ca="1">SUM($B$9:I9)/I3</f>
-        <v>0.3828125</v>
+        <v>0.322265625</v>
       </c>
       <c r="J8" s="68">
         <f ca="1">SUM($B$9:J9)/J3</f>
-        <v>0.45052083333333331</v>
+        <v>0.375</v>
       </c>
       <c r="K8" s="68">
         <f ca="1">SUM($B$9:K9)/K3</f>
-        <v>0.50468749999999996</v>
+        <v>0.39765624999999999</v>
       </c>
       <c r="L8" s="68">
         <f ca="1">SUM($B$9:L9)/L3</f>
-        <v>0.54829545454545459</v>
+        <v>0.38068181818181818</v>
       </c>
       <c r="M8" s="68">
         <f ca="1">SUM($B$9:M9)/M3</f>
-        <v>0.583984375</v>
+        <v>0.38411458333333331</v>
       </c>
       <c r="N8" s="68">
         <f ca="1">SUM($B$9:N9)/N3</f>
-        <v>0.61237980769230771</v>
+        <v>0.41947115384615385</v>
       </c>
       <c r="O8" s="68">
         <f ca="1">SUM($B$9:O9)/O3</f>
-        <v>0.6333705357142857</v>
+        <v>0.43917410714285715</v>
       </c>
       <c r="P8" s="68">
         <f ca="1">SUM($B$9:P9)/P3</f>
-        <v>0.64583333333333337</v>
+        <v>0.43593749999999998</v>
       </c>
       <c r="Q8" s="68">
         <f ca="1">SUM($B$9:Q9)/Q3</f>
-        <v>0.64599609375</v>
+        <v>0.4580078125</v>
       </c>
       <c r="R8" s="68">
         <f ca="1">SUM($B$9:R9)/R3</f>
-        <v>0.62545955882352944</v>
+        <v>0.4655330882352941</v>
       </c>
       <c r="S8" s="68">
         <f ca="1">SUM($B$9:S9)/S3</f>
-        <v>0.62369791666666663</v>
+        <v>0.44965277777777779</v>
       </c>
       <c r="T8" s="68">
         <f ca="1">SUM($B$9:T9)/T3</f>
-        <v>0.60074013157894735</v>
+        <v>0.4453125</v>
       </c>
       <c r="U8" s="68">
         <f ca="1">SUM($B$9:U9)/U3</f>
-        <v>0.58945312500000002</v>
+        <v>0.45976562500000001</v>
       </c>
       <c r="V8" s="68">
         <f ca="1">SUM($B$9:V9)/V3</f>
-        <v>0.5970982142857143</v>
+        <v>0.46056547619047616</v>
       </c>
       <c r="W8" s="68">
         <f ca="1">SUM($B$9:W9)/W3</f>
-        <v>0.59268465909090906</v>
+        <v>0.48330965909090912</v>
       </c>
       <c r="X8" s="68">
         <f ca="1">SUM($B$9:X9)/X3</f>
-        <v>0.56691576086956519</v>
+        <v>0.50271739130434778</v>
       </c>
       <c r="Y8" s="68">
         <f ca="1">SUM($B$9:Y9)/Y3</f>
-        <v>0.54329427083333337</v>
+        <v>0.51790364583333337</v>
       </c>
       <c r="Z8" s="68">
         <f ca="1">SUM($B$9:Z9)/Z3</f>
-        <v>0.52187499999999998</v>
+        <v>0.52687499999999998</v>
       </c>
       <c r="AA8" s="68">
         <f ca="1">SUM($B$9:AA9)/AA3</f>
-        <v>0.50270432692307687</v>
+        <v>0.52524038461538458</v>
       </c>
       <c r="AB8" s="68">
         <f ca="1">SUM($B$9:AB9)/AB3</f>
-        <v>0.48582175925925924</v>
+        <v>0.54195601851851849</v>
       </c>
       <c r="AC8" s="68">
         <f ca="1">SUM($B$9:AC9)/AC3</f>
-        <v>0.47181919642857145</v>
+        <v>0.556640625</v>
       </c>
       <c r="AD8" s="68">
         <f ca="1">SUM($B$9:AD9)/AD3</f>
-        <v>0.46228448275862066</v>
+        <v>0.56896551724137934</v>
       </c>
       <c r="AE8" s="68">
         <f ca="1">SUM($B$9:AE9)/AE3</f>
-        <v>0.46015624999999999</v>
+        <v>0.5776041666666667</v>
       </c>
       <c r="AF8" s="68">
         <f ca="1">SUM($B$9:AF9)/AF3</f>
-        <v>0.47101814516129031</v>
+        <v>0.58014112903225812</v>
       </c>
       <c r="AG8" s="68">
         <f ca="1">SUM($B$9:AG9)/AG3</f>
-        <v>0.474853515625</v>
+        <v>0.572021484375</v>
       </c>
       <c r="AH8" s="68">
         <f ca="1">SUM($B$9:AH9)/AH3</f>
-        <v>0.46614583333333331</v>
+        <v>0.57410037878787878</v>
       </c>
       <c r="AI8" s="68">
         <f ca="1">SUM($B$9:AI9)/AI3</f>
-        <v>0.46346507352941174</v>
+        <v>0.56548713235294112</v>
       </c>
       <c r="AJ8" s="68">
         <f ca="1">SUM($B$9:AJ9)/AJ3</f>
-        <v>0.47165178571428573</v>
+        <v>0.56540178571428568</v>
       </c>
       <c r="AK8" s="68">
         <f ca="1">SUM($B$9:AK9)/AK3</f>
-        <v>0.4724392361111111</v>
+        <v>0.55338541666666663</v>
       </c>
       <c r="AL8" s="68">
         <f ca="1">SUM($B$9:AL9)/AL3</f>
-        <v>0.45967060810810811</v>
+        <v>0.5458192567567568</v>
       </c>
       <c r="AM8" s="68">
         <f ca="1">SUM($B$9:AM9)/AM3</f>
-        <v>0.44757401315789475</v>
+        <v>0.54584703947368418</v>
       </c>
       <c r="AN8" s="68">
         <f ca="1">SUM($B$9:AN9)/AN3</f>
-        <v>0.43609775641025639</v>
+        <v>0.53425480769230771</v>
       </c>
       <c r="AO8" s="68">
         <f ca="1">SUM($B$9:AO9)/AO3</f>
-        <v>0.42519531249999998</v>
+        <v>0.52578124999999998</v>
       </c>
       <c r="AP8" s="68">
         <f ca="1">SUM($B$9:AP9)/AP3</f>
-        <v>0.41501524390243905</v>
+        <v>0.52267530487804881</v>
       </c>
       <c r="AQ8" s="68">
         <f ca="1">SUM($B$9:AQ9)/AQ3</f>
-        <v>0.40550595238095238</v>
+        <v>0.52938988095238093</v>
       </c>
       <c r="AR8" s="68">
         <f ca="1">SUM($B$9:AR9)/AR3</f>
-        <v>0.39680232558139533</v>
+        <v>0.53143168604651159</v>
       </c>
       <c r="AS8" s="68">
         <f ca="1">SUM($B$9:AS9)/AS3</f>
-        <v>0.38920454545454547</v>
+        <v>0.52468039772727271</v>
       </c>
       <c r="AT8" s="68">
         <f ca="1">SUM($B$9:AT9)/AT3</f>
-        <v>0.38333333333333336</v>
+        <v>0.5234375</v>
       </c>
       <c r="AU8" s="68">
         <f ca="1">SUM($B$9:AU9)/AU3</f>
-        <v>0.38060461956521741</v>
+        <v>0.53243885869565222</v>
       </c>
       <c r="AV8" s="68">
         <f ca="1">SUM($B$9:AV9)/AV3</f>
-        <v>0.38347739361702127</v>
+        <v>0.53972739361702127</v>
       </c>
       <c r="AW8" s="68">
         <f ca="1">SUM($B$9:AW9)/AW3</f>
-        <v>0.37630208333333331</v>
+        <v>0.54427083333333337</v>
       </c>
       <c r="AX8" s="68">
         <f ca="1">SUM($B$9:AX9)/AX3</f>
-        <v>0.37021683673469385</v>
+        <v>0.54368622448979587</v>
       </c>
       <c r="AY8" s="68">
         <f ca="1">SUM($B$9:AY9)/AY3</f>
-        <v>0.36609375</v>
+        <v>0.53359374999999998</v>
       </c>
       <c r="AZ8" s="68">
         <f ca="1">SUM($B$9:AZ9)/AZ3</f>
-        <v>0.36534926470588236</v>
+        <v>0.52466299019607843</v>
       </c>
       <c r="BA8" s="68">
         <f ca="1">SUM($B$9:BA9)/BA3</f>
-        <v>0.37109375</v>
+        <v>0.517578125</v>
       </c>
       <c r="BB8" s="68">
         <f ca="1">SUM($B$9:BB9)/BB3</f>
-        <v>0.37043042452830188</v>
+        <v>0.51370872641509435</v>
       </c>
       <c r="BC8" s="68">
         <f ca="1">SUM($B$9:BC9)/BC3</f>
-        <v>0.37601273148148145</v>
+        <v>0.51576967592592593</v>
       </c>
       <c r="BD8" s="68">
         <f ca="1">SUM($B$9:BD9)/BD3</f>
-        <v>0.3755681818181818</v>
+        <v>0.51093750000000004</v>
       </c>
       <c r="BE8" s="68">
         <f ca="1">SUM($B$9:BE9)/BE3</f>
-        <v>0.3814174107142857</v>
+        <v>0.5107421875</v>
       </c>
     </row>
     <row r="9" spans="1:101" x14ac:dyDescent="0.3">
       <c r="B9">
         <f t="shared" ref="B9:BE9" ca="1" si="49">BIN2DEC(B1&amp;C1&amp;D1&amp;E1&amp;F1&amp;G1&amp;H1)/128</f>
-        <v>0.875</v>
+        <v>0.1875</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.5078125</v>
+        <v>0.7578125</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="49"/>
-        <v>2.34375E-2</v>
+        <v>0.5234375</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="49"/>
-        <v>5.46875E-2</v>
+        <v>4.6875E-2</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.1171875</v>
+        <v>9.375E-2</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.2421875</v>
+        <v>0.1953125</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.4921875</v>
+        <v>0.3984375</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.9921875</v>
+        <v>0.796875</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.9921875</v>
+        <v>0.6015625</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.984375</v>
+        <v>0.2109375</v>
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.9765625</v>
+        <v>0.421875</v>
       </c>
       <c r="N9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.953125</v>
+        <v>0.84375</v>
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.90625</v>
+        <v>0.6953125</v>
       </c>
       <c r="P9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.8203125</v>
+        <v>0.390625</v>
       </c>
       <c r="Q9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.6484375</v>
+        <v>0.7890625</v>
       </c>
       <c r="R9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.296875</v>
+        <v>0.5859375</v>
       </c>
       <c r="S9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.59375</v>
+        <v>0.1796875</v>
       </c>
       <c r="T9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.1875</v>
+        <v>0.3671875</v>
       </c>
       <c r="U9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.375</v>
+        <v>0.734375</v>
       </c>
       <c r="V9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.75</v>
+        <v>0.4765625</v>
       </c>
       <c r="W9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.5</v>
+        <v>0.9609375</v>
       </c>
       <c r="X9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>0.9296875</v>
       </c>
       <c r="Y9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>0.8671875</v>
       </c>
       <c r="Z9">
         <f t="shared" ca="1" si="49"/>
-        <v>7.8125E-3</v>
+        <v>0.7421875</v>
       </c>
       <c r="AA9">
         <f t="shared" ca="1" si="49"/>
-        <v>2.34375E-2</v>
+        <v>0.484375</v>
       </c>
       <c r="AB9">
         <f t="shared" ca="1" si="49"/>
-        <v>4.6875E-2</v>
+        <v>0.9765625</v>
       </c>
       <c r="AC9">
         <f t="shared" ca="1" si="49"/>
-        <v>9.375E-2</v>
+        <v>0.953125</v>
       </c>
       <c r="AD9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.1953125</v>
+        <v>0.9140625</v>
       </c>
       <c r="AE9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.3984375</v>
+        <v>0.828125</v>
       </c>
       <c r="AF9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.796875</v>
+        <v>0.65625</v>
       </c>
       <c r="AG9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.59375</v>
+        <v>0.3203125</v>
       </c>
       <c r="AH9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.1875</v>
+        <v>0.640625</v>
       </c>
       <c r="AI9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AJ9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="AK9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.5</v>
+        <v>0.1328125</v>
       </c>
       <c r="AL9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>0.2734375</v>
       </c>
       <c r="AM9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>0.546875</v>
       </c>
       <c r="AN9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>9.375E-2</v>
       </c>
       <c r="AO9">
         <f t="shared" ca="1" si="49"/>
-        <v>0</v>
+        <v>0.1953125</v>
       </c>
       <c r="AP9">
         <f t="shared" ca="1" si="49"/>
-        <v>7.8125E-3</v>
+        <v>0.3984375</v>
       </c>
       <c r="AQ9">
         <f t="shared" ca="1" si="49"/>
-        <v>1.5625E-2</v>
+        <v>0.8046875</v>
       </c>
       <c r="AR9">
         <f t="shared" ca="1" si="49"/>
-        <v>3.125E-2</v>
+        <v>0.6171875</v>
       </c>
       <c r="AS9">
         <f t="shared" ca="1" si="49"/>
-        <v>6.25E-2</v>
+        <v>0.234375</v>
       </c>
       <c r="AT9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.125</v>
+        <v>0.46875</v>
       </c>
       <c r="AU9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.2578125</v>
+        <v>0.9375</v>
       </c>
       <c r="AV9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.515625</v>
+        <v>0.875</v>
       </c>
       <c r="AW9">
         <f t="shared" ca="1" si="49"/>
-        <v>3.90625E-2</v>
+        <v>0.7578125</v>
       </c>
       <c r="AX9">
         <f t="shared" ca="1" si="49"/>
-        <v>7.8125E-2</v>
+        <v>0.515625</v>
       </c>
       <c r="AY9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.1640625</v>
+        <v>3.90625E-2</v>
       </c>
       <c r="AZ9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.328125</v>
+        <v>7.8125E-2</v>
       </c>
       <c r="BA9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.6640625</v>
+        <v>0.15625</v>
       </c>
       <c r="BB9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.3359375</v>
+        <v>0.3125</v>
       </c>
       <c r="BC9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.671875</v>
+        <v>0.625</v>
       </c>
       <c r="BD9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.3515625</v>
+        <v>0.25</v>
       </c>
       <c r="BE9">
         <f t="shared" ca="1" si="49"/>
-        <v>0.703125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:101" x14ac:dyDescent="0.3">
       <c r="B10">
         <f ca="1">(B9-$A$12)^2</f>
-        <v>0.20702500000000001</v>
+        <v>4.9506249999999988E-2</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:BE10" ca="1" si="50">(C9-$A$12)^2</f>
-        <v>0.10890000000000001</v>
+        <v>1.2249999999999982E-3</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="50"/>
-        <v>7.7110351562500032E-3</v>
+        <v>0.12097353515625002</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.15726181640624998</v>
+        <v>1.2868066406250005E-2</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.13345322265624998</v>
+        <v>0.13185976562499999</v>
       </c>
       <c r="G10">
         <f t="shared" ca="1" si="50"/>
-        <v>9.169541015624999E-2</v>
+        <v>0.10001406249999999</v>
       </c>
       <c r="H10">
         <f t="shared" ca="1" si="50"/>
-        <v>3.1617285156249994E-2</v>
+        <v>4.6090722656249992E-2</v>
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.2110351562500027E-3</v>
+        <v>1.3369140624999942E-4</v>
       </c>
       <c r="J10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.32739853515625006</v>
+        <v>0.14967226562500002</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.32739853515625006</v>
+        <v>3.6696191406250009E-2</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.31851914062500009</v>
+        <v>3.9625878906249988E-2</v>
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.30976181640625006</v>
+        <v>1.4101562500000057E-4</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.28422226562500008</v>
+        <v>0.18813906250000001</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.23643906250000002</v>
+        <v>8.140322265625001E-2</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.16025009765625001</v>
+        <v>3.7539062499999904E-4</v>
       </c>
       <c r="Q10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.218369140625001E-2</v>
+        <v>0.14368837890625002</v>
       </c>
       <c r="R10">
         <f t="shared" ca="1" si="50"/>
-        <v>1.5159765624999997E-2</v>
+        <v>3.095400390625001E-2</v>
       </c>
       <c r="S10">
         <f t="shared" ca="1" si="50"/>
-        <v>3.0189062500000006E-2</v>
+        <v>5.304384765624999E-2</v>
       </c>
       <c r="T10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.4056249999999993E-2</v>
+        <v>1.8329101562499978E-3</v>
       </c>
       <c r="U10">
         <f t="shared" ca="1" si="50"/>
-        <v>2.0249999999999986E-3</v>
+        <v>0.10521914062500001</v>
       </c>
       <c r="V10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.10890000000000001</v>
+        <v>4.4305664062500036E-3</v>
       </c>
       <c r="W10">
         <f t="shared" ca="1" si="50"/>
-        <v>6.4000000000000029E-3</v>
+        <v>0.30353212890625009</v>
       </c>
       <c r="X10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>0.2700750976562501</v>
       </c>
       <c r="Y10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>0.20902041015625003</v>
       </c>
       <c r="Z10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.16989853515624997</v>
+        <v>0.11034853515625001</v>
       </c>
       <c r="AA10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.15726181640624998</v>
+        <v>5.531640625000004E-3</v>
       </c>
       <c r="AB10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.13922226562499998</v>
+        <v>0.32099306640625008</v>
       </c>
       <c r="AC10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.10643906249999999</v>
+        <v>0.29498476562500009</v>
       </c>
       <c r="AD10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.0484472656249994E-2</v>
+        <v>0.2540790039062501</v>
       </c>
       <c r="AE10">
         <f t="shared" ca="1" si="50"/>
-        <v>4.6494140624999932E-4</v>
+        <v>0.17482851562500001</v>
       </c>
       <c r="AF10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.142034765625</v>
+        <v>6.0639062500000014E-2</v>
       </c>
       <c r="AG10">
         <f t="shared" ca="1" si="50"/>
-        <v>3.0189062500000006E-2</v>
+        <v>8.0438476562499951E-3</v>
       </c>
       <c r="AH10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.4056249999999993E-2</v>
+        <v>5.3187890625000012E-2</v>
       </c>
       <c r="AI10">
         <f t="shared" ca="1" si="50"/>
-        <v>2.0249999999999986E-3</v>
+        <v>1.6576562499999992E-2</v>
       </c>
       <c r="AJ10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.10890000000000001</v>
+        <v>2.3256250000000006E-2</v>
       </c>
       <c r="AK10">
         <f t="shared" ca="1" si="50"/>
-        <v>6.4000000000000029E-3</v>
+        <v>7.6832910156249989E-2</v>
       </c>
       <c r="AL10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>1.8649316406249995E-2</v>
       </c>
       <c r="AM10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>1.8734765625000007E-2</v>
       </c>
       <c r="AN10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>0.10001406249999999</v>
       </c>
       <c r="AO10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.17639999999999997</v>
+        <v>4.6090722656249992E-2</v>
       </c>
       <c r="AP10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.16989853515624997</v>
+        <v>1.3369140624999942E-4</v>
       </c>
       <c r="AQ10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.16351914062499998</v>
+        <v>0.15577822265625002</v>
       </c>
       <c r="AR10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.15112656249999998</v>
+        <v>4.2926660156250011E-2</v>
       </c>
       <c r="AS10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.12780624999999998</v>
+        <v>3.0844140624999992E-2</v>
       </c>
       <c r="AT10">
         <f t="shared" ca="1" si="50"/>
-        <v>8.7024999999999991E-2</v>
+        <v>3.4515625000000028E-3</v>
       </c>
       <c r="AU10">
         <f t="shared" ca="1" si="50"/>
-        <v>2.6304785156249996E-2</v>
+        <v>0.27825625000000009</v>
       </c>
       <c r="AV10">
         <f t="shared" ca="1" si="50"/>
-        <v>9.1441406250000034E-3</v>
+        <v>0.21622500000000003</v>
       </c>
       <c r="AW10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.14511337890624998</v>
+        <v>0.12097353515625002</v>
       </c>
       <c r="AX10">
         <f t="shared" ca="1" si="50"/>
-        <v>0.11687851562499998</v>
+        <v>1.1156640625000006E-2</v>
       </c>
       <c r="AY10">
         <f t="shared" ca="1" si="50"/>
-        <v>6.5504003906249997E-2</v>
+        <v>0.13759462890624999</v>
       </c>
       <c r="AZ10">
         <f t="shared" ca="1" si="50"/>
-        <v>8.4410156249999976E-3</v>
+        <v>0.11014101562499998</v>
       </c>
       <c r="BA10">
         <f t="shared" ca="1" si="50"/>
-        <v>5.9566503906250005E-2</v>
+        <v>6.4389062499999983E-2</v>
       </c>
       <c r="BB10">
         <f t="shared" ca="1" si="50"/>
-        <v>7.0665039062499978E-3</v>
+        <v>9.5062499999999956E-3</v>
       </c>
       <c r="BC10">
         <f t="shared" ca="1" si="50"/>
-        <v>6.3441015625000013E-2</v>
+        <v>4.6225000000000009E-2</v>
       </c>
       <c r="BD10">
         <f t="shared" ca="1" si="50"/>
-        <v>4.6836914062499983E-3</v>
+        <v>2.5599999999999991E-2</v>
       </c>
       <c r="BE10">
         <f t="shared" ca="1" si="50"/>
-        <v>8.0159765625000004E-2</v>
+        <v>8.1000000000000048E-3</v>
       </c>
     </row>
     <row r="11" spans="1:101" x14ac:dyDescent="0.3">
@@ -55013,7 +56889,7 @@
     <row r="12" spans="1:101" x14ac:dyDescent="0.3">
       <c r="A12">
         <f ca="1">B7</f>
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AA12">
         <v>26</v>
@@ -55022,7 +56898,7 @@
     <row r="13" spans="1:101" x14ac:dyDescent="0.3">
       <c r="A13">
         <f ca="1">SQRT(SUM(B10:BE10)/(100-1))</f>
-        <v>0.25200675411448437</v>
+        <v>0.22303266018914802</v>
       </c>
       <c r="C13">
         <v>84</v>
